--- a/nexus_river_view_master.xlsx
+++ b/nexus_river_view_master.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Master_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Directors_Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Petty_Cash" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transactions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Banks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Bank_Transactions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Installments" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Customer_Installments" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Directors_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petty_Cash" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Banks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank_Transactions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Installments" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer_Installments" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -846,7 +846,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -858,7 +858,7 @@
         <v>100000</v>
       </c>
       <c r="J12" t="n">
-        <v>-100000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="13">
@@ -1504,7 +1504,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>100000</v>
       </c>
       <c r="J29" t="n">
-        <v>100000</v>
+        <v>-100000</v>
       </c>
     </row>
     <row r="30">
@@ -2027,17 +2027,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="143" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="196" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2112,7 +2112,11 @@
       <c r="G2" t="n">
         <v>900</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2144,7 +2148,11 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2176,7 +2184,11 @@
       <c r="G4" t="n">
         <v>600</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2208,7 +2220,11 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2240,7 +2256,11 @@
       <c r="G6" t="n">
         <v>300</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2272,7 +2292,11 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2304,7 +2328,11 @@
       <c r="G8" t="n">
         <v>6000</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2336,7 +2364,11 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2368,7 +2400,11 @@
       <c r="G10" t="n">
         <v>-3340</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2400,7 +2436,11 @@
       <c r="G11" t="n">
         <v>-9840</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2432,7 +2472,11 @@
       <c r="G12" t="n">
         <v>-29840</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2464,7 +2508,11 @@
       <c r="G13" t="n">
         <v>-30400</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2474,12 +2522,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Check Withdrawal</t>
+          <t>Contra CN1:  (Transfer from Bank)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Contra</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2528,7 +2576,11 @@
       <c r="G15" t="n">
         <v>-1900</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2560,7 +2612,11 @@
       <c r="G16" t="n">
         <v>-400</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2592,7 +2648,11 @@
       <c r="G17" t="n">
         <v>-540</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2624,7 +2684,11 @@
       <c r="G18" t="n">
         <v>-830</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2656,7 +2720,11 @@
       <c r="G19" t="n">
         <v>-3830</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2688,7 +2756,11 @@
       <c r="G20" t="n">
         <v>-830</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2720,7 +2792,11 @@
       <c r="G21" t="n">
         <v>-930</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2752,7 +2828,11 @@
       <c r="G22" t="n">
         <v>-4110</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2784,7 +2864,11 @@
       <c r="G23" t="n">
         <v>-1110</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2816,7 +2900,11 @@
       <c r="G24" t="n">
         <v>-12065</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2848,7 +2936,11 @@
       <c r="G25" t="n">
         <v>-1110</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2880,7 +2972,11 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2890,7 +2986,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Withdraw from Bank</t>
+          <t>Computer, Printer &amp; Scanner Purchase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2900,19 +2996,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>60600</v>
       </c>
       <c r="G27" t="n">
-        <v>80000</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>-60600</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>computerset.webp</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2922,7 +3022,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Computer, Printer &amp; Scanner Purchase</t>
+          <t>Stationery and Office Supplies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2939,14 +3039,14 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>60600</v>
+        <v>725</v>
       </c>
       <c r="G28" t="n">
-        <v>19400</v>
+        <v>-61325</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>computerset.png</t>
+          <t>stationary.webp</t>
         </is>
       </c>
     </row>
@@ -2975,14 +3075,14 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>725</v>
+        <v>1530</v>
       </c>
       <c r="G29" t="n">
-        <v>18675</v>
+        <v>-62855</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stationary.png</t>
+          <t>stationary2.webp</t>
         </is>
       </c>
     </row>
@@ -2994,7 +3094,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Stationery and Office Supplies</t>
+          <t>Multi Plug Purchase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3011,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1530</v>
+        <v>650</v>
       </c>
       <c r="G30" t="n">
-        <v>17145</v>
+        <v>-63505</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stationary2.png</t>
+          <t>multiplug.webp</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3130,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Multi Plug Purchase</t>
+          <t>Conveyance for PC Purchase and Others</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3047,14 +3147,14 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>650</v>
+        <v>170</v>
       </c>
       <c r="G31" t="n">
-        <v>16495</v>
+        <v>-63675</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>multiplug.png</t>
+          <t>img20260203_18140907.webp</t>
         </is>
       </c>
     </row>
@@ -3066,33 +3166,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Conveyance for PC Purchase and Others</t>
+          <t>Contra CN2: Computer and others (Transfer from Bank)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Contra</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F32" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>16325</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>img20260203_18140907.png</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3126,7 +3222,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>basket.png</t>
+          <t>basket.webp</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3256,11 @@
       <c r="G34" t="n">
         <v>1565</v>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3192,7 +3292,11 @@
       <c r="G35" t="n">
         <v>1205</v>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3202,7 +3306,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Withdraw from Bank</t>
+          <t>Office Rent (February-26) and Stuff Salary</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3212,21 +3316,21 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
         <v>26500</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
       <c r="G36" t="n">
-        <v>27705</v>
+        <v>-25295</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>WhatsApp_Image_2026-02-04_at_11.35.32_AM.jpeg</t>
+          <t>.webp</t>
         </is>
       </c>
     </row>
@@ -3238,24 +3342,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Office Rent (February-26) and Stuff Salary</t>
+          <t>Contra CN3: Salary and house rent of February  (Transfer from Bank)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Contra</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>26500</v>
       </c>
       <c r="F37" t="n">
-        <v>26500</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>1205</v>
@@ -3292,7 +3396,11 @@
       <c r="G38" t="n">
         <v>1055</v>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3326,7 +3434,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>WhatsApp_Image_2026-02-15_at_2.41.33_PM.jpeg</t>
+          <t>WhatsApp_Image_2026-02-15_at_2.41.33_PM.webp</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3470,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>WhatsApp_Image_2026-02-15_at_2.41.33_PM.jpeg</t>
+          <t>WhatsApp_Image_2026-02-15_at_2.41.33_PM.webp</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3506,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WhatsApp_Image_2026-02-18_at_12.09.36_PM.jpeg</t>
+          <t>WhatsApp_Image_2026-02-18_at_12.09.36_PM.webp</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3540,11 @@
       <c r="G42" t="n">
         <v>1120</v>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3464,22 +3576,26 @@
       <c r="G43" t="n">
         <v>620</v>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cash Withdraw</t>
+          <t>Contra CN4: Salary and house rent for February and others (Transfer from Bank)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Contra</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3506,9 +3622,9 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Voucher DV-20260311-0001: Shariful Islam -Salary+Phone Bill -20500 |
-Masud - Salary+Phone Bill - 3500 |
-Shahzahan - 1500 |
+          <t>Voucher DV-20260311-0001: Shariful Islam -Salary+Phone Bill -20500 |
+Masud - Salary+Phone Bill - 3500 |
+Shahzahan - 1500 |
 Md Rimon -1500|</t>
         </is>
       </c>
@@ -3669,7 +3785,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Voucher DV-20260311-0006: Rickshaw fare to Jahid Sir's office for check signing</t>
+          <t>Voucher DV-20260311-0006: Rickshaw fare to Jahid Sir's office for cheque signing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3696,34 +3812,701 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Contra CN5: For iftar party, lawyer's fee  (Transfer from Bank)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Contra</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>22500</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>22480</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Voucher DV7: Lawyer's Fee</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
         <v>3000</v>
       </c>
-      <c r="G51" t="n">
-        <v>-3020</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>19480</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Voucher DV8: Expense for Iftar</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>480</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Voucher DV15: Design fee advance to Arman</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-99520</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Contra CN10: Design fee advance to Arman (Transfer from Bank)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Contra</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>480</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Voucher DV10: House Rent for April</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>House Rent</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-19520</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Voucher DV11: Electricity Bill for March</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>500</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-20020</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Contra CN6: For house Rent of April (20000) and Electricity bill for March (500) (Transfer from Bank)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Contra</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>480</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>WhatsApp_Image_2026-04-07_at_1.21.57_PM_20260407_152955_795092.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voucher DV12: Conveyance for Signing cheque from Jahid sir </t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Conveyance</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>80</v>
+      </c>
+      <c r="G59" t="n">
+        <v>400</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Contra CN7: Shariful's salary and phone bill for the month of March 2026 (Transfer from Bank)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Contra</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>20900</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>WhatsApp_Image_2026-04-08_at_5.27.51_PM_20260408_173216_126640.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Contra CN8: The 5,000 BDT (Eid bonus of Shariful) provided by Arif Sir has been reimbursed; out of the total 6,500 BDT, the remaining 1,500 BDT has been kept as petty cash." (Transfer from Bank)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Contra</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>27400</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>WhatsApp_Image_2026-04-08_at_5.34.04_PM_20260408_174501_566640.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Contra CN9: Electricity connection cost: 17,636, and 364 has been kept as petty cash. (Transfer from Bank)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Contra</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>45400</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>WhatsApp_Image_2026-04-08_at_5.35.52_PM_20260408_174959_670350.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Voucher DV13: Electricity connection cost</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>17636</v>
+      </c>
+      <c r="G63" t="n">
+        <v>27764</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Voucher DV16: Conveyance for visiting electricity office</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Conveyance</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>80</v>
+      </c>
+      <c r="G64" t="n">
+        <v>27684</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Voucher DV14: "Eid bonus of Shariful provided by Arif Sir has been reimbursed</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G65" t="n">
+        <v>22684</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voucher DV17: Shariful’s salary is 20,000, and the phone bill is 500.
+</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>20500</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2184</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voucher DV18: Conveyance for going to Jahid Sir’s office and then Electric Office for the transformer.
+</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Conveyance</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>140</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Voucher DV19: Salary of March (Masud - 3000 |Shahjahan - 1500 |Md Rimon -1500)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Salary</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-3956</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Contra CN11:  salary of march (Masud - 3000  | Shahzahan - 1500 |Md Rimon -1500) (Transfer from Bank)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Contra</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2044</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>WhatsApp_Image_2026-04-13_at_12.18.06_PM_20260413_162612_364032.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Contra CN12: For Electric transformer.
+ (Transfer from Bank)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Contra</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>74044</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>WhatsApp_Image_2026-04-13_at_12.18.07_PM_20260413_162708_143456.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Voucher DV20: Three guests have been entertained</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>150</v>
+      </c>
+      <c r="G71" t="n">
+        <v>73894</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3841,7 +4624,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3881,7 +4668,11 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3921,7 +4712,11 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3961,7 +4756,11 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4001,7 +4800,11 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4041,7 +4844,11 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4081,7 +4888,11 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4121,7 +4932,11 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4161,7 +4976,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4201,7 +5020,11 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4241,7 +5064,11 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4277,7 +5104,11 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4317,7 +5148,11 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4357,7 +5192,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4397,7 +5236,11 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4437,7 +5280,11 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4473,7 +5320,11 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4513,7 +5364,11 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4553,7 +5408,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4593,7 +5452,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4633,7 +5496,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4673,7 +5540,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4713,7 +5584,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4753,7 +5628,11 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4793,7 +5672,11 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4833,7 +5716,11 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4873,7 +5760,11 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4913,7 +5804,11 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4953,7 +5848,11 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4993,7 +5892,11 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5033,7 +5936,11 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5073,7 +5980,11 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5113,7 +6024,11 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>.webp</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5300,7 +6215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5352,7 +6267,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02-02-2026</t>
+          <t>05-02-2026</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -5363,21 +6278,25 @@
           <t>United Commercial Bank PLC</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>RTGS</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G2" t="n">
-        <v>3340645.49</v>
+        <v>3440645.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05-02-2026</t>
+          <t>09-02-2026</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5390,23 +6309,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RTGS</t>
+          <t>Banking Fund Transfer - Credit</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>3440645.49</v>
+        <v>3640645.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09-02-2026</t>
+          <t>10-12-2025</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5419,23 +6338,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Banking Fund Transfer - Credit</t>
+          <t>Trn. Br: 084 Cash Deposit</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="G4" t="n">
-        <v>3640645.49</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10-02-2026</t>
+          <t>16-02-2026</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5448,23 +6367,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>For Salary and Rent</t>
+          <t>Banking Fund Transfer - Credit</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26500</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G5" t="n">
-        <v>3614145.49</v>
+        <v>3714145.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10-12-2025</t>
+          <t>16-02-2026</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5477,23 +6396,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 Cash Deposit</t>
+          <t>Cash Deposit</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1000</v>
+        <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3914145.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11-03-2026</t>
+          <t>18-12-2025</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5506,23 +6425,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>For Salary -House -Rent -Electick -Arif sir+ Acc</t>
+          <t>Trn. Br: 138 Cash Deposit</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56950</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G7" t="n">
-        <v>4757195.49</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14-01-2026</t>
+          <t>19-01-2026</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5535,23 +6454,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 Cheque Withdrawal</t>
+          <t>Trn. Br: 000 000245******0000 IBBLOMNI 000840207655</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G8" t="n">
-        <v>20655.49000000001</v>
+        <v>70655.49000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16-02-2026</t>
+          <t>20-01-2026</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5564,23 +6483,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Banking Fund Transfer - Credit</t>
+          <t>Trn. Br: 000 000245******0000 90001000 000840527911</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>3714145.49</v>
+        <v>270655.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16-02-2026</t>
+          <t>20-01-2026</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5593,7 +6512,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash Deposit</t>
+          <t>Trn. Br: 000 000245******0000 90001000 000840528466</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -5603,13 +6522,13 @@
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>3914145.49</v>
+        <v>470655.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18-12-2025</t>
+          <t>20-01-2026</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -5622,23 +6541,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Trn. Br: 138 Cash Deposit</t>
+          <t>Trn. Br: 084 MDAJIJUR RAHMAN 0100200190160 DILHARMIN-ID: B13526019X772010 _JANATA BANK LTD..HEAD OFFICE</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G11" t="n">
-        <v>51000</v>
+        <v>570655.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19-01-2026</t>
+          <t>20-01-2026</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5651,17 +6570,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 IBBLOMNI 000840207655</t>
+          <t>Trn. Br: 084 MDAJIJUR RAHMAN 0100200190160 AJIJUR RAHMAN-ID: B13526019U261582 _JANATA BANK LTD..HEAD OFFICE</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G12" t="n">
-        <v>70655.49000000001</v>
+        <v>670655.49</v>
       </c>
     </row>
     <row r="13">
@@ -5680,7 +6599,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 90001000 000840527911</t>
+          <t>Trn. Br: 084 JANBBDDH, DHAKA COLLEGE GATE, MD MOHIDUL ISLAM - Nexus River View</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -5690,7 +6609,7 @@
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>270655.49</v>
+        <v>870655.49</v>
       </c>
     </row>
     <row r="14">
@@ -5709,17 +6628,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 90001000 000840528466</t>
+          <t>Trn. Br: 000 000245******0000 IBBLOMNI 000840708177</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="G14" t="n">
-        <v>470655.49</v>
+        <v>920655.49</v>
       </c>
     </row>
     <row r="15">
@@ -5738,17 +6657,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 MDAJIJUR RAHMAN 0100200190160 DILHARMIN-ID: B13526019X772010 _JANATA BANK LTD..HEAD OFFICE</t>
+          <t>Trn. Br: 000 000245******0000 61000765 000840714780</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>570655.49</v>
+        <v>1120655.49</v>
       </c>
     </row>
     <row r="16">
@@ -5767,17 +6686,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 MDAJIJUR RAHMAN 0100200190160 AJIJUR RAHMAN-ID: B13526019U261582 _JANATA BANK LTD..HEAD OFFICE</t>
+          <t>Trn. Br: 084 BSONBDDH, BUET Branch, Aparna Bali - INTELECT</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>670655.49</v>
+        <v>1320655.49</v>
       </c>
     </row>
     <row r="17">
@@ -5796,7 +6715,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 JANBBDDH, DHAKA COLLEGE GATE, MD MOHIDUL ISLAM - Nexus River View</t>
+          <t>Trn. Br: 000 000245******0000 NPSBIBFT 000841001652</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -5806,7 +6725,7 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>870655.49</v>
+        <v>1520655.49</v>
       </c>
     </row>
     <row r="18">
@@ -5825,23 +6744,23 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 IBBLOMNI 000840708177</t>
+          <t>Trn. Br: 120 IB(Unet) Nexus Riverview Payment</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>920655.49</v>
+        <v>1720655.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20-01-2026</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5854,23 +6773,23 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 61000765 000840714780</t>
+          <t>Contra CN1: Transfer to Cash</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="F19" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1120655.49</v>
+        <v>20655.49000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20-01-2026</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5883,23 +6802,23 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 BSONBDDH, BUET Branch, Aparna Bali - INTELECT</t>
+          <t>Contra CN2: Transfer to Cash</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F20" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1320655.49</v>
+        <v>3340645.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20-01-2026</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5912,23 +6831,23 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 NPSBIBFT 000841001652</t>
+          <t>Contra CN3: Transfer to Cash</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>26500</v>
       </c>
       <c r="F21" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1520655.49</v>
+        <v>3614145.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20-01-2026</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5941,7 +6860,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Trn. Br: 120 IB(Unet) Nexus Riverview Payment</t>
+          <t>Banking Fund Transfer - Credit</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -5951,13 +6870,13 @@
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>1720655.49</v>
+        <v>4114145.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5977,16 +6896,16 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="G23" t="n">
-        <v>4114145.49</v>
+        <v>4814145.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5999,23 +6918,23 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Banking Fund Transfer - Credit</t>
+          <t>Contra CN4: Transfer to Cash</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>56950</v>
       </c>
       <c r="F24" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>4814145.49</v>
+        <v>4757195.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21-01-2026</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6028,23 +6947,23 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 00600009 000841231133</t>
+          <t>Contra CN5: Transfer to Cash</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="F25" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1820655.49</v>
+        <v>4734695.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21-01-2026</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6057,23 +6976,23 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 AGBKBDDH, JATIYA PRESS CLUB, MD ATAUR RAHMAN CHOWDHURY - PAYMENT - SCCT</t>
+          <t>Contra CN10: Transfer to Cash</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="F26" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1920655.49</v>
+        <v>4634695.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21-01-2026</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6086,23 +7005,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 IBBLBDDH, UTTARA, Shahidul Islam -</t>
+          <t>Contra CN6: Transfer to Cash</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="F27" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2020655.49</v>
+        <v>4614195.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>22-01-2026</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6115,23 +7034,23 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 00600009 000842082313</t>
+          <t>Contra CN7: Transfer to Cash</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="F28" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2120655.49</v>
+        <v>4593695.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>22-12-2025</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6144,23 +7063,23 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Trn. Br: 084</t>
+          <t>Contra CN8: Transfer to Cash</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>300</v>
+        <v>6500</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>50700</v>
+        <v>4587195.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>22-12-2025</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6173,23 +7092,23 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Trn. Br: 084</t>
+          <t>Contra CN9: Transfer to Cash</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>45</v>
+        <v>18000</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>50655</v>
+        <v>4569195.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25-01-2026</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6202,23 +7121,23 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 IBBLBDDH, FENI, MOHAMMED JAHIR ULLAH -</t>
+          <t>Contra CN11: Transfer to Cash</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="F31" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2320655.49</v>
+        <v>4563195.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>25-02-2026</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6231,23 +7150,23 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Banking Fund Transfer - Credit</t>
+          <t>Contra CN12: Transfer to Cash</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="F32" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>4214145.49</v>
+        <v>4491195.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26-01-2026</t>
+          <t>21-01-2026</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6260,7 +7179,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 ISLAMI BANK BANGLDESH LTD., AGENT BANKING Related Account: 0843201000809046</t>
+          <t>Trn. Br: 000 000245******0000 00600009 000841231133</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -6270,13 +7189,13 @@
         <v>100000</v>
       </c>
       <c r="G33" t="n">
-        <v>2420655.49</v>
+        <v>1820655.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>26-01-2026</t>
+          <t>21-01-2026</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6289,23 +7208,23 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 ISLAMI BANK BANGLDESH LTD., AGENT BANKING Related Account: 0843201000809046</t>
+          <t>Trn. Br: 084 AGBKBDDH, JATIYA PRESS CLUB, MD ATAUR RAHMAN CHOWDHURY - PAYMENT - SCCT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G34" t="n">
-        <v>2420645.49</v>
+        <v>1920655.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26-01-2026</t>
+          <t>21-01-2026</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6318,23 +7237,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Trn. Br: 777 IB(Unet) pay</t>
+          <t>Trn. Br: 084 IBBLBDDH, UTTARA, Shahidul Islam -</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="G35" t="n">
-        <v>2620645.49</v>
+        <v>2020655.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26-02-2026</t>
+          <t>22-01-2026</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6347,23 +7266,23 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Banking Fund Transfer - Credit</t>
+          <t>Trn. Br: 000 000245******0000 00600009 000842082313</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="G36" t="n">
-        <v>4714145.49</v>
+        <v>2120655.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>22-12-2025</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6376,23 +7295,23 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 SUMIYA BINTE SHAHID 2706101119862 Alimuzzman-ID: B17526027A326697 _Pubali Bank PLC, TRUNCATION POINT</t>
+          <t>Trn. Br: 084</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F37" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2710645.49</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>22-12-2025</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6405,23 +7324,23 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 ALIMUZZAMAN 1161030187123 Alimuzzman-ID: B09026027A030590 _Dutch-Bangla Bank PLC,LOCAL OFFICE</t>
+          <t>Trn. Br: 084</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F38" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2820645.49</v>
+        <v>50655</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>25-01-2026</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6434,23 +7353,23 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 SUSMITA DAS 0100007463043 1st Installment N-ID: B13526027O074980 _JANATA BANK LTD..HEAD OFFICE</t>
+          <t>Trn. Br: 084 IBBLBDDH, FENI, MOHAMMED JAHIR ULLAH -</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>2920645.49</v>
+        <v>2320655.49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>25-02-2026</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6463,7 +7382,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Trn. Br: 000 000245******0000 90001000 000845920253</t>
+          <t xml:space="preserve">	Banking Fund Transfer - Credit</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -6473,13 +7392,13 @@
         <v>100000</v>
       </c>
       <c r="G40" t="n">
-        <v>3020645.49</v>
+        <v>4214145.49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>31-01-2026</t>
+          <t>26-01-2026</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6492,23 +7411,23 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Trn. Br: 786 EB (Unet)businesses</t>
+          <t>Trn. Br: 084 ISLAMI BANK BANGLDESH LTD., AGENT BANKING Related Account: 0843201000809046</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="G41" t="n">
-        <v>3320645.49</v>
+        <v>2420655.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>31-01-2026</t>
+          <t>26-01-2026</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6521,23 +7440,23 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Trn. Br: 786 EB (Unet)Business</t>
+          <t>Trn. Br: 084 ISLAMI BANK BANGLDESH LTD., AGENT BANKING Related Account: 0843201000809046</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>3420645.49</v>
+        <v>2420645.49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>31-12-2025</t>
+          <t>26-01-2026</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6550,23 +7469,23 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Trn. Br: 084 Related Account: 0843201000809046</t>
+          <t>Trn. Br: 777 IB(Unet) pay</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.58</v>
+        <v>200000</v>
       </c>
       <c r="G43" t="n">
-        <v>50655.58</v>
+        <v>2620645.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>31-12-2025</t>
+          <t>26-02-2026</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6579,16 +7498,248 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>Banking Fund Transfer - Credit</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4714145.49</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>28-01-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Trn. Br: 084 SUMIYA BINTE SHAHID 2706101119862 Alimuzzman-ID: B17526027A326697 _Pubali Bank PLC, TRUNCATION POINT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2710645.49</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>28-01-2026</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Trn. Br: 084 ALIMUZZAMAN 1161030187123 Alimuzzman-ID: B09026027A030590 _Dutch-Bangla Bank PLC,LOCAL OFFICE</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>110000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2820645.49</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>28-01-2026</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Trn. Br: 084 SUSMITA DAS 0100007463043 1st Installment N-ID: B13526027O074980 _JANATA BANK LTD..HEAD OFFICE</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2920645.49</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>28-01-2026</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Trn. Br: 000 000245******0000 90001000 000845920253</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3020645.49</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>31-01-2026</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Trn. Br: 786 EB (Unet)businesses</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3320645.49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>31-01-2026</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Trn. Br: 786 EB (Unet)Business</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3420645.49</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>31-12-2025</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>Trn. Br: 084 Related Account: 0843201000809046</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G51" t="n">
+        <v>50655.58</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>31-12-2025</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>United Commercial Bank PLC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Trn. Br: 084 Related Account: 0843201000809046</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
         <v>0.09</v>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
         <v>50655.49000000001</v>
       </c>
     </row>
@@ -7414,13 +8565,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>100000</v>
       </c>
       <c r="F29" t="n">
-        <v>100000</v>
+        <v>-100000</v>
       </c>
     </row>
     <row r="30">
@@ -7440,13 +8591,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="E30" t="n">
         <v>100000</v>
       </c>
       <c r="F30" t="n">
-        <v>-100000</v>
+        <v>100000</v>
       </c>
     </row>
   </sheetData>
